--- a/MUQABIL_Practice_History_Test_Candidate_2026-10-12.xlsx
+++ b/MUQABIL_Practice_History_Test_Candidate_2026-10-12.xlsx
@@ -425,7 +425,7 @@
         <v>Export Date</v>
       </c>
       <c r="B3" t="str">
-        <v>10/12/2026, 1:50:12 PM</v>
+        <v>10/12/2026, 1:58:15 PM</v>
       </c>
     </row>
     <row r="4">
